--- a/Mussel_heartrate_module/Mussel_heartrate_module_parts.xlsx
+++ b/Mussel_heartrate_module/Mussel_heartrate_module_parts.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915DCB61-AEB4-427D-A15A-E70C750253F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BE80B3-1D33-43C3-BC9C-FF719D2E95DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39740" yWindow="1400" windowWidth="30060" windowHeight="14480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2150" windowWidth="30470" windowHeight="18850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RevC" sheetId="3" r:id="rId1"/>
     <sheet name="RevA-B" sheetId="1" r:id="rId2"/>
-    <sheet name="Reference_design" sheetId="2" r:id="rId3"/>
+    <sheet name="RevD" sheetId="4" r:id="rId3"/>
+    <sheet name="Reference_design" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,6 +26,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="104">
   <si>
     <t>Description</t>
   </si>
@@ -205,9 +207,6 @@
     <t>2368-47-23348-CL-ND</t>
   </si>
   <si>
-    <t>Clear heat shrink - adhesive lined 3/8 diameter</t>
-  </si>
-  <si>
     <t>47-23348-CL</t>
   </si>
   <si>
@@ -220,9 +219,6 @@
     <t>MAX30101EFD+</t>
   </si>
   <si>
-    <t>MAX30101EFD+-ND</t>
-  </si>
-  <si>
     <t>HeartRate Sensor RevC parts</t>
   </si>
   <si>
@@ -301,9 +297,6 @@
     <t>Alternate Digikey PN</t>
   </si>
   <si>
-    <t>MAX30100EFD+TCT-ND</t>
-  </si>
-  <si>
     <t>296-46571-1-ND</t>
   </si>
   <si>
@@ -316,7 +309,43 @@
     <t>NCP508SQ18T1G</t>
   </si>
   <si>
-    <t>MAX30100EFD+</t>
+    <t>MAX30101EFD+TCT-ND</t>
+  </si>
+  <si>
+    <t>MAX30102EFD+TCT-ND</t>
+  </si>
+  <si>
+    <t>MAX30102</t>
+  </si>
+  <si>
+    <t>Clear heat shrink - adhesive lined 3/8 diameter, 4-foot piece</t>
+  </si>
+  <si>
+    <t>3M156160-ND</t>
+  </si>
+  <si>
+    <t>EPS300-3/8-48"-CLEAR-125 PCS</t>
+  </si>
+  <si>
+    <t>Also order - bulk materials 1 piece will cover many sensors</t>
+  </si>
+  <si>
+    <t>HeartRate Sensor RevD parts</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>MAXM86161AEFD+T</t>
+  </si>
+  <si>
+    <t>175-MAXM86161AEFD+TCT-ND</t>
+  </si>
+  <si>
+    <t>MAXM86161A heart sensor</t>
+  </si>
+  <si>
+    <t>Original MAXM86161 superceded by MAXM86161A model in 2026</t>
   </si>
 </sst>
 </file>
@@ -681,7 +710,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -711,16 +740,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -735,16 +764,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
@@ -759,16 +788,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" s="5">
         <v>2</v>
@@ -783,16 +812,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E6" s="5">
         <v>2</v>
@@ -810,10 +839,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -831,16 +860,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
         <v>81</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -855,7 +884,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G10" s="4">
         <f>SUM(G3:G8)</f>
@@ -874,7 +903,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J13"/>
+  <dimension ref="A2:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.08984375" bestFit="1" customWidth="1"/>
@@ -888,7 +917,7 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -914,37 +943,37 @@
         <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>12</v>
+        <v>10.09</v>
       </c>
       <c r="G4" s="1">
         <f>F4*E4</f>
-        <v>12</v>
+        <v>10.09</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -968,10 +997,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -995,10 +1024,10 @@
         <v>0.13</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -1121,24 +1150,35 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-    </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="3">
         <f>SUM(G4:G11)</f>
-        <v>14.940000000000001</v>
+        <v>13.030000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1149,6 +1189,122 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{483565D2-5A9B-4567-BBA9-4B21AD4CE250}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="31.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5" si="0">F5*E5</f>
+        <v>0.27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
